--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92569622867</v>
+        <v>46157.93103797861</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93103797861</v>
+        <v>46157.9317519053</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9317519053</v>
+        <v>46157.93401206883</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93401206883</v>
+        <v>46157.9371916813</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9371916813</v>
+        <v>46158.28217374838</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28217374838</v>
+        <v>46158.29683095654</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29683095654</v>
+        <v>46158.29816033162</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29816033162</v>
+        <v>46158.33388389066</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33388389066</v>
+        <v>46158.36858203082</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/2. ИП Мамедов Фариз (мойка)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36858203082</v>
+        <v>46158.37288865793</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
